--- a/Peterhof/восстановление/!восстановление_подписи_текст4.xlsx
+++ b/Peterhof/восстановление/!восстановление_подписи_текст4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Disk E\arhiv_site\Петергоф_выкладка\восстановления\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\liferay-ce-portal-7.2.1-ga2\PeterhoffParts\Peterhoff\Peterhof\восстановление\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB41C617-8AD9-41C7-8808-BCFD573CFCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890E08C8-DCDD-412D-998E-76402E0DF71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" tabRatio="949" firstSheet="15" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29145" yWindow="3240" windowWidth="18540" windowHeight="11385" tabRatio="949" firstSheet="15" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1969,7 +1969,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2260,13 +2260,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -2274,12 +2274,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -2407,130 +2407,130 @@
         <v>413</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="14"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
     </row>
@@ -2545,13 +2545,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>191</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>192</v>
       </c>
@@ -2602,13 +2602,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>193</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>194</v>
       </c>
@@ -2659,13 +2659,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="76.36328125" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="76.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>195</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>196</v>
       </c>
@@ -2716,13 +2716,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="67.90625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="67.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>40</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>45</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>72</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>49</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>50</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>52</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>53</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>55</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>56</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>57</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>58</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>59</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>60</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>61</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>62</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>63</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>64</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>65</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>66</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>67</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>68</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>69</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>70</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>71</v>
       </c>
@@ -3037,13 +3037,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="78.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="78.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>75</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>76</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>77</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>78</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>79</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
@@ -3150,13 +3150,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>82</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>83</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>84</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>85</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>86</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>87</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>88</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>89</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>90</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>91</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>92</v>
       </c>
@@ -3279,13 +3279,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3293,12 +3293,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>94</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>95</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>96</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>97</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>98</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>99</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>100</v>
       </c>
@@ -3370,53 +3370,53 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="14"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
   </sheetData>
@@ -3430,13 +3430,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>372</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>373</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>374</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>375</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>376</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>377</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>378</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>379</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>380</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>381</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>382</v>
       </c>
@@ -3559,13 +3559,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="95.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="95.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>180</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>181</v>
       </c>
@@ -3616,13 +3616,13 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3630,12 +3630,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>184</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>211</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>212</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>213</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>214</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>215</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>216</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>217</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>218</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>219</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>220</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>221</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>222</v>
       </c>
@@ -3747,7 +3747,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>224</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>225</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>225</v>
       </c>
@@ -3790,13 +3790,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>414</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>415</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>417</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>416</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>418</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>419</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>420</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>421</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
@@ -3899,13 +3899,13 @@
     <tabColor rgb="FF6CC9D6"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3913,12 +3913,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>102</v>
       </c>
@@ -3945,13 +3945,13 @@
     <tabColor rgb="FF6CC9D6"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>101</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>352</v>
       </c>
@@ -3994,13 +3994,13 @@
     <tabColor rgb="FF6CC9D6"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="137.36328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="137.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>101</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>103</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>104</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>105</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>106</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>107</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>108</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>109</v>
       </c>
@@ -4091,13 +4091,13 @@
     <tabColor rgb="FF6CC9D6"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>101</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>111</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>112</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>113</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
@@ -4172,13 +4172,13 @@
     <tabColor rgb="FF6CC9D6"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="90.6328125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="90.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>101</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>208</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>209</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>210</v>
       </c>
@@ -4237,13 +4237,13 @@
     <tabColor rgb="FFBD92DE"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4251,12 +4251,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>116</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>121</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>123</v>
       </c>
@@ -4307,13 +4307,13 @@
     <tabColor rgb="FFBD92DE"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>115</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>118</v>
       </c>
@@ -4364,13 +4364,13 @@
     <tabColor rgb="FFBD92DE"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>115</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>119</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>120</v>
       </c>
@@ -4421,13 +4421,13 @@
     <tabColor rgb="FFBD92DE"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>115</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>206</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>207</v>
       </c>
@@ -4478,13 +4478,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4492,12 +4492,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>125</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>126</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>127</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>128</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>131</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>135</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>136</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>139</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>140</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>141</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>142</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>154</v>
       </c>
@@ -4612,13 +4612,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>422</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>423</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>428</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>427</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>426</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>425</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="203" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="225" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>424</v>
       </c>
@@ -4709,13 +4709,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>324</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>325</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>326</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>327</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>328</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="116" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>329</v>
       </c>
@@ -4798,13 +4798,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>323</v>
       </c>
@@ -4847,13 +4847,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>129</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>130</v>
       </c>
@@ -4904,13 +4904,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>132</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>133</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>134</v>
       </c>
@@ -4969,13 +4969,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>137</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>138</v>
       </c>
@@ -5026,13 +5026,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>143</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>144</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>145</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>146</v>
       </c>
@@ -5099,13 +5099,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5113,7 +5113,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>147</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>148</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>149</v>
       </c>
@@ -5164,13 +5164,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>150</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>151</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>152</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>153</v>
       </c>
@@ -5237,13 +5237,13 @@
     <tabColor rgb="FFFF7C80"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>124</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>197</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>198</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>199</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>200</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>201</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>202</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>203</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>204</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>205</v>
       </c>
@@ -5350,13 +5350,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5364,12 +5364,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>156</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>157</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>158</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>159</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>160</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>161</v>
       </c>
@@ -5436,13 +5436,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>249</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>250</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>251</v>
       </c>
@@ -5501,13 +5501,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>155</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>47</v>
       </c>
@@ -5558,13 +5558,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>155</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>175</v>
       </c>
@@ -5596,7 +5596,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>176</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>177</v>
       </c>
@@ -5623,13 +5623,13 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>155</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>182</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>183</v>
       </c>
@@ -5680,13 +5680,13 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5694,12 +5694,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>162</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>163</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>164</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>165</v>
       </c>
@@ -5750,13 +5750,13 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>287</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>302</v>
       </c>
@@ -5799,13 +5799,13 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>166</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>167</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>168</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>169</v>
       </c>
@@ -5864,13 +5864,13 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>166</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>170</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>171</v>
       </c>
@@ -5921,13 +5921,13 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>166</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>172</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>173</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>174</v>
       </c>
@@ -5986,13 +5986,13 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>166</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>178</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>179</v>
       </c>
@@ -6043,13 +6043,13 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>166</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>187</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>188</v>
       </c>
@@ -6100,13 +6100,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -6166,13 +6166,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -6236,7 +6236,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -6303,13 +6303,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -6325,7 +6325,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -6360,13 +6360,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>185</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>186</v>
       </c>
@@ -6417,13 +6417,13 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="58.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>247</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>189</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>190</v>
       </c>
